--- a/data/trans_orig/P1410-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1410-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de trastornos cardíacos en 2007</t>
+          <t>Población con diagnóstico de trastornos cardíacos en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19935</t>
+          <t>18886</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41111</t>
+          <t>38881</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20774</t>
+          <t>19806</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42372</t>
+          <t>41428</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45082</t>
+          <t>45210</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>73996</t>
+          <t>74843</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>652901</t>
+          <t>655131</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>674077</t>
+          <t>675126</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>645979</t>
+          <t>646923</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>667577</t>
+          <t>668545</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1308367</t>
+          <t>1307520</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1337281</t>
+          <t>1337153</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,73%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28557</t>
+          <t>30588</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55725</t>
+          <t>57124</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27202</t>
+          <t>26397</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51271</t>
+          <t>52530</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>61975</t>
+          <t>62481</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>98638</t>
+          <t>97539</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>906075</t>
+          <t>904676</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>933243</t>
+          <t>931212</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>917122</t>
+          <t>915863</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>941191</t>
+          <t>941996</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1831555</t>
+          <t>1832654</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1868218</t>
+          <t>1867712</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,76%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25704</t>
+          <t>26438</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49329</t>
+          <t>49198</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22402</t>
+          <t>22573</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46156</t>
+          <t>45451</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54396</t>
+          <t>52577</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>84606</t>
+          <t>87112</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>629180</t>
+          <t>629311</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>652805</t>
+          <t>652071</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>637685</t>
+          <t>638390</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>661439</t>
+          <t>661268</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1277744</t>
+          <t>1275238</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1307954</t>
+          <t>1309773</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,14%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33742</t>
+          <t>33139</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58744</t>
+          <t>59015</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18009</t>
+          <t>19193</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38775</t>
+          <t>39790</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>56642</t>
+          <t>56141</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>88223</t>
+          <t>89102</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>883478</t>
+          <t>883207</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>908480</t>
+          <t>909083</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>999837</t>
+          <t>998822</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1020603</t>
+          <t>1019419</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1892611</t>
+          <t>1891732</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1924192</t>
+          <t>1924693</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,17%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>130747</t>
+          <t>128507</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>174841</t>
+          <t>175060</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>105804</t>
+          <t>105205</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>151020</t>
+          <t>150696</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>246944</t>
+          <t>244433</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>308669</t>
+          <t>310370</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3101702</t>
+          <t>3101483</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3145796</t>
+          <t>3148036</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3228177</t>
+          <t>3228501</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3273393</t>
+          <t>3273992</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6347072</t>
+          <t>6345371</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6408797</t>
+          <t>6411308</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,33%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de trastornos cardíacos en 2012</t>
+          <t>Población con diagnóstico de trastornos cardíacos en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15560</t>
+          <t>15869</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35672</t>
+          <t>36185</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22921</t>
+          <t>22827</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44960</t>
+          <t>45542</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42561</t>
+          <t>43570</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>74262</t>
+          <t>73000</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>667797</t>
+          <t>667284</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>687909</t>
+          <t>687600</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>652090</t>
+          <t>651508</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>674129</t>
+          <t>674223</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1326257</t>
+          <t>1327519</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1357958</t>
+          <t>1356949</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,89%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28599</t>
+          <t>28263</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53709</t>
+          <t>52717</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32035</t>
+          <t>32393</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57720</t>
+          <t>58047</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>65946</t>
+          <t>67418</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>104320</t>
+          <t>104107</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>964238</t>
+          <t>965230</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>989348</t>
+          <t>989684</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>970071</t>
+          <t>969744</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>995756</t>
+          <t>995398</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1941418</t>
+          <t>1941631</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1979792</t>
+          <t>1978320</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,7%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17093</t>
+          <t>16656</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40356</t>
+          <t>39812</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14036</t>
+          <t>14345</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33399</t>
+          <t>33718</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36202</t>
+          <t>36464</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64767</t>
+          <t>65475</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>717267</t>
+          <t>717811</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>740530</t>
+          <t>740967</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>743775</t>
+          <t>743456</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>763138</t>
+          <t>762829</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1470030</t>
+          <t>1469322</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1498595</t>
+          <t>1498333</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,62%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31768</t>
+          <t>30963</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57072</t>
+          <t>56821</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37129</t>
+          <t>37008</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65164</t>
+          <t>64530</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>73355</t>
+          <t>75116</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>111178</t>
+          <t>111592</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>890667</t>
+          <t>890918</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>915971</t>
+          <t>916776</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>986737</t>
+          <t>987371</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1014772</t>
+          <t>1014893</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1888462</t>
+          <t>1888048</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1926285</t>
+          <t>1924524</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,24%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>111422</t>
+          <t>111254</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>157498</t>
+          <t>153947</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>125454</t>
+          <t>126734</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>173005</t>
+          <t>174749</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>246614</t>
+          <t>248326</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>316933</t>
+          <t>314820</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3269281</t>
+          <t>3272832</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3315357</t>
+          <t>3315525</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3380911</t>
+          <t>3379167</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3428462</t>
+          <t>3427182</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6663761</t>
+          <t>6665874</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6734080</t>
+          <t>6732368</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,44%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de trastornos cardíacos en 2016</t>
+          <t>Población con diagnóstico de trastornos cardíacos en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19854</t>
+          <t>18859</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39390</t>
+          <t>39236</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31474</t>
+          <t>31638</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>59888</t>
+          <t>58070</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>56612</t>
+          <t>56195</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>90897</t>
+          <t>92880</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>635410</t>
+          <t>635564</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>654946</t>
+          <t>655941</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>612951</t>
+          <t>614769</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>641365</t>
+          <t>641201</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1256742</t>
+          <t>1254759</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1291027</t>
+          <t>1291444</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,83%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28489</t>
+          <t>28629</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53711</t>
+          <t>53086</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23604</t>
+          <t>22943</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48664</t>
+          <t>47476</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>58317</t>
+          <t>58366</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>92457</t>
+          <t>92731</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>968720</t>
+          <t>969345</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>993942</t>
+          <t>993802</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>994249</t>
+          <t>995437</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1019309</t>
+          <t>1019970</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1972887</t>
+          <t>1972613</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2007027</t>
+          <t>2006978</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,17%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19842</t>
+          <t>20338</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41950</t>
+          <t>42442</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24635</t>
+          <t>25371</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49565</t>
+          <t>50206</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49908</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>83670</t>
+          <t>83253</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>717602</t>
+          <t>717110</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>739710</t>
+          <t>739214</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>735446</t>
+          <t>734805</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>760376</t>
+          <t>759640</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1460893</t>
+          <t>1461310</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1494655</t>
+          <t>1494563</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,76%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20822</t>
+          <t>20284</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41620</t>
+          <t>40036</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32913</t>
+          <t>33652</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61423</t>
+          <t>62254</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>59304</t>
+          <t>59198</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>95470</t>
+          <t>95784</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>895947</t>
+          <t>897531</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>916745</t>
+          <t>917283</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>982356</t>
+          <t>981525</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1010866</t>
+          <t>1010127</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1885876</t>
+          <t>1885562</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1922042</t>
+          <t>1922148</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>104181</t>
+          <t>105577</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>149380</t>
+          <t>150123</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>133561</t>
+          <t>134252</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>184543</t>
+          <t>187856</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>253079</t>
+          <t>255287</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>320581</t>
+          <t>322397</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3244970</t>
+          <t>3244227</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3290169</t>
+          <t>3288773</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3359999</t>
+          <t>3356686</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3410981</t>
+          <t>3410290</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6618311</t>
+          <t>6616495</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6685813</t>
+          <t>6683605</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,32%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de trastornos cardíacos en 2023</t>
+          <t>Población con diagnóstico de trastornos cardíacos en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26515</t>
+          <t>26851</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47261</t>
+          <t>46773</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27993</t>
+          <t>27256</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46140</t>
+          <t>45935</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59215</t>
+          <t>58702</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86680</t>
+          <t>85984</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>586860</t>
+          <t>587348</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>607606</t>
+          <t>607270</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>629230</t>
+          <t>629435</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>647377</t>
+          <t>648114</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1222811</t>
+          <t>1223507</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1250276</t>
+          <t>1250789</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,52%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24127</t>
+          <t>23416</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61097</t>
+          <t>62385</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33654</t>
+          <t>33808</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51871</t>
+          <t>52857</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>60118</t>
+          <t>58236</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>104847</t>
+          <t>104863</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1131767</t>
+          <t>1130479</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1168737</t>
+          <t>1169448</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>905566</t>
+          <t>904580</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>923783</t>
+          <t>923629</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2045454</t>
+          <t>2045438</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2090183</t>
+          <t>2092065</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32208</t>
+          <t>32222</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62090</t>
+          <t>60884</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10073</t>
+          <t>11186</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35605</t>
+          <t>35868</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43208</t>
+          <t>46207</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89481</t>
+          <t>88816</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>640875</t>
+          <t>642081</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>670757</t>
+          <t>670743</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>895790</t>
+          <t>895527</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>921322</t>
+          <t>920209</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1544878</t>
+          <t>1545543</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1591151</t>
+          <t>1588152</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,17%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41296</t>
+          <t>42958</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66863</t>
+          <t>66771</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34116</t>
+          <t>33821</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60163</t>
+          <t>57793</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>83762</t>
+          <t>80647</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>115944</t>
+          <t>116710</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>859968</t>
+          <t>860060</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>885535</t>
+          <t>883873</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1031353</t>
+          <t>1033723</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1057400</t>
+          <t>1057695</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1902403</t>
+          <t>1901637</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1934585</t>
+          <t>1937700</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>96,0%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>139462</t>
+          <t>132194</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>207281</t>
+          <t>204021</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>121721</t>
+          <t>124331</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>170024</t>
+          <t>172075</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>283106</t>
+          <t>279511</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>361099</t>
+          <t>363416</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3249500</t>
+          <t>3252760</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3317319</t>
+          <t>3324587</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3485694</t>
+          <t>3483643</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3533997</t>
+          <t>3531387</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6751400</t>
+          <t>6749083</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6829393</t>
+          <t>6832988</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,07%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1410-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1410-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18886</t>
+          <t>18852</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38881</t>
+          <t>38838</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19806</t>
+          <t>20607</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41428</t>
+          <t>41607</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45210</t>
+          <t>45581</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>74843</t>
+          <t>74632</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>655131</t>
+          <t>655174</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>675126</t>
+          <t>675160</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>646923</t>
+          <t>646744</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>668545</t>
+          <t>667744</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1307520</t>
+          <t>1307731</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1337153</t>
+          <t>1336782</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,7%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30588</t>
+          <t>30293</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57124</t>
+          <t>55347</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26397</t>
+          <t>26696</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52530</t>
+          <t>52027</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>62481</t>
+          <t>62121</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>97539</t>
+          <t>99051</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>904676</t>
+          <t>906453</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>931212</t>
+          <t>931507</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>915863</t>
+          <t>916366</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>941996</t>
+          <t>941697</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1832654</t>
+          <t>1831142</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1867712</t>
+          <t>1868072</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,78%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26438</t>
+          <t>24897</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49198</t>
+          <t>49066</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,82 +1434,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>3,67%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7,23%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>31962</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>21907</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>44361</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>4,67%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>6,49%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>68097</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>53161</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>86616</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>5,0%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>3,9%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,25%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>31962</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>22573</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>45451</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>4,67%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>3,3%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>6,65%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>68097</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>52577</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>87112</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>5,0%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>3,86%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>629311</t>
+          <t>629443</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>652071</t>
+          <t>653612</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,82 +1547,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>96,33%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>664</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>651879</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>639480</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>661934</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>95,33%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>93,51%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>96,8%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1269</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1294253</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1275734</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1309189</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>95,0%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>93,64%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>96,1%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>664</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>651879</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>638390</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>661268</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>95,33%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>93,35%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>96,7%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1269</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1294253</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>1275238</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1309773</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>95,0%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>93,61%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>96,14%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33139</t>
+          <t>33155</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59015</t>
+          <t>56780</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19193</t>
+          <t>18764</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39790</t>
+          <t>38561</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>56141</t>
+          <t>57268</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>89102</t>
+          <t>87864</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>883207</t>
+          <t>885442</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>909083</t>
+          <t>909067</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>998822</t>
+          <t>1000051</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1019419</t>
+          <t>1019848</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1891732</t>
+          <t>1892970</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1924693</t>
+          <t>1923566</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,11%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>128507</t>
+          <t>128162</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>175060</t>
+          <t>176137</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>105205</t>
+          <t>106550</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>150696</t>
+          <t>149062</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>244433</t>
+          <t>246647</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>310370</t>
+          <t>309740</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3101483</t>
+          <t>3100406</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3148036</t>
+          <t>3148381</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3228501</t>
+          <t>3230135</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3273992</t>
+          <t>3272647</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6345371</t>
+          <t>6346001</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6411308</t>
+          <t>6409094</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,29%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15869</t>
+          <t>15641</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36185</t>
+          <t>34509</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22827</t>
+          <t>22831</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45542</t>
+          <t>44860</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43570</t>
+          <t>43209</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>73000</t>
+          <t>72192</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>667284</t>
+          <t>668960</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>687600</t>
+          <t>687828</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>651508</t>
+          <t>652190</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>674223</t>
+          <t>674219</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1327519</t>
+          <t>1328327</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1356949</t>
+          <t>1357310</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,91%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28263</t>
+          <t>28552</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52717</t>
+          <t>53492</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32393</t>
+          <t>32063</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58047</t>
+          <t>58818</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>67418</t>
+          <t>65847</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>104107</t>
+          <t>103359</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>965230</t>
+          <t>964455</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>989684</t>
+          <t>989395</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>969744</t>
+          <t>968973</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>995398</t>
+          <t>995728</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1941631</t>
+          <t>1942379</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1978320</t>
+          <t>1979891</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,78%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16656</t>
+          <t>17628</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39812</t>
+          <t>39979</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14345</t>
+          <t>13880</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33718</t>
+          <t>34653</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36464</t>
+          <t>36637</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65475</t>
+          <t>66021</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>717811</t>
+          <t>717644</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>740967</t>
+          <t>739995</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>743456</t>
+          <t>742521</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>762829</t>
+          <t>763294</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1469322</t>
+          <t>1468776</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1498333</t>
+          <t>1498160</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30963</t>
+          <t>30904</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56821</t>
+          <t>55840</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37008</t>
+          <t>35859</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64530</t>
+          <t>62864</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>75116</t>
+          <t>74338</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>111592</t>
+          <t>111252</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>890918</t>
+          <t>891899</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>916776</t>
+          <t>916835</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>987371</t>
+          <t>989037</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1014893</t>
+          <t>1016042</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1888048</t>
+          <t>1888388</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1924524</t>
+          <t>1925302</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,28%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>111254</t>
+          <t>111168</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>153947</t>
+          <t>157690</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>126734</t>
+          <t>125933</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>174749</t>
+          <t>174392</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>248326</t>
+          <t>250073</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>314820</t>
+          <t>315456</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3272832</t>
+          <t>3269089</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3315525</t>
+          <t>3315611</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3379167</t>
+          <t>3379524</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3427182</t>
+          <t>3427983</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6665874</t>
+          <t>6665238</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6732368</t>
+          <t>6730621</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,42%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18859</t>
+          <t>19841</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39236</t>
+          <t>40754</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31638</t>
+          <t>29850</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58070</t>
+          <t>58125</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>56195</t>
+          <t>56289</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>92880</t>
+          <t>90479</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>635564</t>
+          <t>634046</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>655941</t>
+          <t>654959</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>614769</t>
+          <t>614714</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>641201</t>
+          <t>642989</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1254759</t>
+          <t>1257160</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1291444</t>
+          <t>1291350</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,82%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28629</t>
+          <t>28785</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53086</t>
+          <t>52525</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22943</t>
+          <t>24058</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47476</t>
+          <t>48522</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>58366</t>
+          <t>59040</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>92731</t>
+          <t>94502</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>969345</t>
+          <t>969906</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>993802</t>
+          <t>993646</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>995437</t>
+          <t>994391</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1019970</t>
+          <t>1018855</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1972613</t>
+          <t>1970842</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2006978</t>
+          <t>2006304</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,14%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20338</t>
+          <t>20760</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42442</t>
+          <t>42166</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25371</t>
+          <t>24210</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50206</t>
+          <t>50324</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>50695</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>83253</t>
+          <t>82021</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>717110</t>
+          <t>717386</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>739214</t>
+          <t>738792</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>734805</t>
+          <t>734687</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>759640</t>
+          <t>760801</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1461310</t>
+          <t>1462542</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1494563</t>
+          <t>1493868</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,72%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20284</t>
+          <t>20154</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40036</t>
+          <t>41101</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33652</t>
+          <t>33122</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62254</t>
+          <t>60840</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>59198</t>
+          <t>58961</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>95784</t>
+          <t>94959</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>897531</t>
+          <t>896466</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>917283</t>
+          <t>917413</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>981525</t>
+          <t>982939</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1010127</t>
+          <t>1010657</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1885562</t>
+          <t>1886387</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1922148</t>
+          <t>1922385</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,02%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>105577</t>
+          <t>106988</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>150123</t>
+          <t>151519</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>134252</t>
+          <t>134684</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>187856</t>
+          <t>187085</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>255287</t>
+          <t>255624</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>322397</t>
+          <t>324470</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3244227</t>
+          <t>3242831</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3288773</t>
+          <t>3287362</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3356686</t>
+          <t>3357457</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3410290</t>
+          <t>3409858</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6616495</t>
+          <t>6614422</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6683605</t>
+          <t>6683268</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>35765</t>
+          <t>39234</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26851</t>
+          <t>28943</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46773</t>
+          <t>50377</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>35402</t>
+          <t>37754</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27256</t>
+          <t>30133</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45935</t>
+          <t>49475</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>71167</t>
+          <t>76988</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>58702</t>
+          <t>64347</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85984</t>
+          <t>94234</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>598356</t>
+          <t>650095</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>587348</t>
+          <t>638952</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>607270</t>
+          <t>660386</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>639968</t>
+          <t>694968</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>629435</t>
+          <t>683247</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>648114</t>
+          <t>702589</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1238324</t>
+          <t>1345063</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1223507</t>
+          <t>1327817</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1250789</t>
+          <t>1357704</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,48%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>634121</t>
+          <t>689329</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>634121</t>
+          <t>689329</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>634121</t>
+          <t>689329</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1309491</t>
+          <t>1422051</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1309491</t>
+          <t>1422051</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1309491</t>
+          <t>1422051</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>43849</t>
+          <t>47650</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23416</t>
+          <t>35578</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62385</t>
+          <t>61366</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>42196</t>
+          <t>47290</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33808</t>
+          <t>37675</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52857</t>
+          <t>58159</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>86044</t>
+          <t>94940</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>58236</t>
+          <t>81811</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>104863</t>
+          <t>114511</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1149015</t>
+          <t>1001267</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1130479</t>
+          <t>987551</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1169448</t>
+          <t>1013339</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>915241</t>
+          <t>1022897</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>904580</t>
+          <t>1012028</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>923629</t>
+          <t>1032512</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2064257</t>
+          <t>2024164</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2045438</t>
+          <t>2004593</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2092065</t>
+          <t>2037293</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>96,14%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>957437</t>
+          <t>1070187</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>957437</t>
+          <t>1070187</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>957437</t>
+          <t>1070187</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2150301</t>
+          <t>2119104</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2150301</t>
+          <t>2119104</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2150301</t>
+          <t>2119104</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>44128</t>
+          <t>47829</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32222</t>
+          <t>35983</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60884</t>
+          <t>63017</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>24350</t>
+          <t>27840</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11186</t>
+          <t>19944</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35868</t>
+          <t>38365</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>68478</t>
+          <t>75670</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46207</t>
+          <t>61519</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>88816</t>
+          <t>95818</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>658837</t>
+          <t>753388</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>642081</t>
+          <t>738200</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>670743</t>
+          <t>765234</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>907045</t>
+          <t>781772</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>895527</t>
+          <t>771247</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>920209</t>
+          <t>789668</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1565881</t>
+          <t>1535159</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1545543</t>
+          <t>1515011</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1588152</t>
+          <t>1549310</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>96,18%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>702965</t>
+          <t>801217</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>702965</t>
+          <t>801217</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>702965</t>
+          <t>801217</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>931395</t>
+          <t>809612</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>931395</t>
+          <t>809612</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>931395</t>
+          <t>809612</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1634359</t>
+          <t>1610829</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1634359</t>
+          <t>1610829</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1634359</t>
+          <t>1610829</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>53218</t>
+          <t>56251</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42958</t>
+          <t>44498</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66771</t>
+          <t>70072</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>45647</t>
+          <t>50144</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33821</t>
+          <t>40710</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57793</t>
+          <t>62437</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>98865</t>
+          <t>106395</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>80647</t>
+          <t>90048</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>116710</t>
+          <t>122843</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>873613</t>
+          <t>933811</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>860060</t>
+          <t>919990</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>883873</t>
+          <t>945564</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1045869</t>
+          <t>1067089</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1033723</t>
+          <t>1054796</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1057695</t>
+          <t>1076523</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1919482</t>
+          <t>2000900</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1901637</t>
+          <t>1984452</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1937700</t>
+          <t>2017247</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,73%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1091516</t>
+          <t>1117233</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1091516</t>
+          <t>1117233</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1091516</t>
+          <t>1117233</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2018347</t>
+          <t>2107295</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2018347</t>
+          <t>2107295</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2018347</t>
+          <t>2107295</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>176960</t>
+          <t>190965</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>132194</t>
+          <t>166361</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>204021</t>
+          <t>216189</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>147595</t>
+          <t>163028</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>124331</t>
+          <t>143315</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>172075</t>
+          <t>183498</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>324555</t>
+          <t>353993</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>279511</t>
+          <t>323764</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>363416</t>
+          <t>388032</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3279821</t>
+          <t>3338561</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3252760</t>
+          <t>3313337</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3324587</t>
+          <t>3363165</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3508123</t>
+          <t>3566726</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3483643</t>
+          <t>3546256</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3531387</t>
+          <t>3586439</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6787944</t>
+          <t>6905287</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6749083</t>
+          <t>6871248</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6832988</t>
+          <t>6935516</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,54%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3456781</t>
+          <t>3529526</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3456781</t>
+          <t>3529526</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3456781</t>
+          <t>3529526</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3655718</t>
+          <t>3729754</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3655718</t>
+          <t>3729754</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3655718</t>
+          <t>3729754</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7112499</t>
+          <t>7259280</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7112499</t>
+          <t>7259280</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7112499</t>
+          <t>7259280</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
